--- a/Results/single_algorithm/Spectrum/Spectrum_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/single_algorithm/Spectrum/Spectrum_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">SpectrumSpectrum2</t>
+    <t xml:space="preserve">Spectrum2</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">SpectrumSpectrum1</t>
+    <t xml:space="preserve">Spectrum1</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
